--- a/output/勤務変更管理システム.xlsx
+++ b/output/勤務変更管理システム.xlsx
@@ -11,12 +11,13 @@
     <sheet name="申請" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="承認" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="ロールバック" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="履歴" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="職員マスタ" sheetId="6" state="veryHidden" r:id="rId6"/>
-    <sheet name="設定" sheetId="7" state="veryHidden" r:id="rId7"/>
+    <sheet name="交換申請" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="履歴" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="職員マスタ" sheetId="7" state="veryHidden" r:id="rId7"/>
+    <sheet name="設定" sheetId="8" state="veryHidden" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'履歴'!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'履歴'!$A$1:$L$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1476,7 +1477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1486,6 +1487,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1552,25 +1554,30 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
+          <t>対象者</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
           <t>対象日</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>変更前</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>変更後</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>変更理由</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>申請日時</t>
         </is>
@@ -1595,7 +1602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1605,6 +1612,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1668,25 +1676,30 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
+          <t>対象者</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
           <t>対象日</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>変更前</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>変更後(現在値)</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>承認者</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>承認日時</t>
         </is>
@@ -1706,7 +1719,138 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2000"/>
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>勤務交換申請(2名間の振替)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>申請者氏名</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>パスワード</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>【対象者A】氏名</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>対象日A</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>現在の勤務A(自動表示)</t>
+        </is>
+      </c>
+      <c r="B8" s="9">
+        <f>IFERROR(INDEX(シフト表!$B$5:$AF$200,MATCH($B$7,シフト表!$A$5:$A$200,0),MATCH(DAY($B$8),シフト表!$B$3:$AF$3,0)),"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>変更後の勤務A</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>【対象者B】氏名</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>対象日B</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>現在の勤務B(自動表示)</t>
+        </is>
+      </c>
+      <c r="B13" s="9">
+        <f>IFERROR(INDEX(シフト表!$B$5:$AF$200,MATCH($B$12,シフト表!$A$5:$A$200,0),MATCH(DAY($B$13),シフト表!$B$3:$AF$3,0)),"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>変更後の勤務B</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>交換理由(任意)</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>入力後、下の「交換を申請する」ボタンを押してください。(ボタンは初回に自動作成されます)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="8D79"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A18:F18"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L2000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1720,6 +1864,7 @@
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1740,40 +1885,45 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
+          <t>対象者</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
           <t>対象日</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>変更前</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>変更後</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>変更理由</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>ステータス</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>承認者</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>承認/処理日時</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>元申請ID(ロールバック用)</t>
         </is>
@@ -3780,12 +3930,12 @@
     <row r="2000"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="8D79"/>
-  <autoFilter ref="A1:K1"/>
+  <autoFilter ref="A1:L1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3833,7 +3983,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
